--- a/Plotting/Results_excels/result_data_long_Scope1-3_FPO.xlsx
+++ b/Plotting/Results_excels/result_data_long_Scope1-3_FPO.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:S126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,27 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -535,6 +556,51 @@
           <t>2050</t>
         </is>
       </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -559,32 +625,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20250910_15_09\Iteration_1\20250910185800_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_1\20251116182215_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20250910_15_09\Iteration_1\20250910195747_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_1\20251116191504_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20250910_15_09\Iteration_1\20250911044025_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_1\20251117025450_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20250910_15_09\Iteration_2\20250911083608_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_2\20251117063704_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20250910_15_09\Iteration_2\20250911093648_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_2\20251117071651_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20250910_15_09\Iteration_2\20250912033725_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_2\20251117112644_2050_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_3\20251117154758_2030_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_3\20251117163022_2040_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_3\20251117204053_2050_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_4\20251118002120_2030_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_4\20251118010854_2040_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_4\20251118055522_2050_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_5\20251118095843_2030_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_5\20251118104351_2040_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-3\Results_model_linking_20251116_14_55\Iteration_5\20251118163637_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
     </row>
@@ -604,22 +715,49 @@
         <v>1588224754.870359</v>
       </c>
       <c r="E5" t="n">
-        <v>3791924679.558226</v>
+        <v>3796931848.461641</v>
       </c>
       <c r="F5" t="n">
-        <v>2538303502.765468</v>
+        <v>2545126301.239653</v>
       </c>
       <c r="G5" t="n">
-        <v>2270454268.272862</v>
+        <v>2141399856.464623</v>
       </c>
       <c r="H5" t="n">
-        <v>3801808651.978255</v>
+        <v>3819341190.024753</v>
       </c>
       <c r="I5" t="n">
-        <v>2532546916.640487</v>
+        <v>2620595894.394333</v>
       </c>
       <c r="J5" t="n">
-        <v>2289927878.662002</v>
+        <v>2305160967.080594</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3818809331.98729</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2618926945.188227</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2306012956.980045</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3819692409.574564</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2609977992.354858</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2302356699.454638</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3818461229.670853</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2619907547.804677</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2308178263.098683</v>
       </c>
     </row>
     <row r="6">
@@ -637,17 +775,38 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>414644950.9304218</v>
+        <v>413589516.8382394</v>
       </c>
       <c r="G6" t="n">
-        <v>580087670.2271032</v>
+        <v>578831007.9934403</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>410971763.9501538</v>
+        <v>418703377.3260342</v>
       </c>
       <c r="J6" t="n">
-        <v>577853464.2593596</v>
+        <v>682109918.2160547</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>418719706.6945889</v>
+      </c>
+      <c r="M6" t="n">
+        <v>683267706.613533</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>417433058.0967261</v>
+      </c>
+      <c r="P6" t="n">
+        <v>615299630.8181607</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>418258137.4471096</v>
+      </c>
+      <c r="S6" t="n">
+        <v>681425050.1120546</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +825,49 @@
         <v>1967451280.173568</v>
       </c>
       <c r="E7" t="n">
-        <v>3791924679.558226</v>
+        <v>3796931848.461641</v>
       </c>
       <c r="F7" t="n">
-        <v>2952948453.69589</v>
+        <v>2958715818.077892</v>
       </c>
       <c r="G7" t="n">
-        <v>2850541938.499965</v>
+        <v>2720230864.458063</v>
       </c>
       <c r="H7" t="n">
-        <v>3801808651.978255</v>
+        <v>3819341190.024753</v>
       </c>
       <c r="I7" t="n">
-        <v>2943518680.590641</v>
+        <v>3039299271.720367</v>
       </c>
       <c r="J7" t="n">
-        <v>2867781342.921362</v>
+        <v>2987270885.296649</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3818809331.98729</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3037646651.882816</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2989280663.593578</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3819692409.574564</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3027411050.451584</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2917656330.272799</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3818461229.670853</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3038165685.251787</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2989603313.210737</v>
       </c>
     </row>
     <row r="8">
@@ -698,12 +884,27 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>91807701208.23659</v>
+        <v>90622890141.59357</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>92021369115.40105</v>
+        <v>94272079697.15735</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>94270169407.69095</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>93473267322.0222</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>94279720906.86267</v>
       </c>
     </row>
     <row r="9">
@@ -722,22 +923,49 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6303822.827622563</v>
+        <v>6313340.78405435</v>
       </c>
       <c r="F9" t="n">
-        <v>3151911.413811286</v>
+        <v>3156670.392027163</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6301202.697411807</v>
+        <v>8014877.675039769</v>
       </c>
       <c r="I9" t="n">
-        <v>3150601.348705976</v>
+        <v>3620128.603078488</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.116655766963959e-06</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8004309.893569999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3637384.429648497</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8050909.950109462</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4025454.975054713</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8036702.380252719</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3618070.911640354</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.532056093215942e-07</v>
       </c>
     </row>
     <row r="10">
@@ -756,22 +984,49 @@
         <v>109669566.8429292</v>
       </c>
       <c r="E10" t="n">
-        <v>414644950.9304218</v>
+        <v>413589516.8382394</v>
       </c>
       <c r="F10" t="n">
-        <v>165442719.2966814</v>
+        <v>165241491.1552009</v>
       </c>
       <c r="G10" t="n">
-        <v>109258752.2597099</v>
+        <v>115048159.6567163</v>
       </c>
       <c r="H10" t="n">
-        <v>410971763.9501538</v>
+        <v>418703377.3260342</v>
       </c>
       <c r="I10" t="n">
-        <v>166881700.3092058</v>
+        <v>263406540.8900205</v>
       </c>
       <c r="J10" t="n">
-        <v>109184630.0324524</v>
+        <v>138091314.0847658</v>
+      </c>
+      <c r="K10" t="n">
+        <v>418719706.6945889</v>
+      </c>
+      <c r="L10" t="n">
+        <v>264547999.9189441</v>
+      </c>
+      <c r="M10" t="n">
+        <v>137909938.7849176</v>
+      </c>
+      <c r="N10" t="n">
+        <v>417433058.0967261</v>
+      </c>
+      <c r="O10" t="n">
+        <v>197866572.7214345</v>
+      </c>
+      <c r="P10" t="n">
+        <v>132721828.4665351</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>418258137.4471096</v>
+      </c>
+      <c r="R10" t="n">
+        <v>263166912.664945</v>
+      </c>
+      <c r="S10" t="n">
+        <v>138468863.1022869</v>
       </c>
     </row>
     <row r="11">
@@ -790,22 +1045,49 @@
         <v>234380321.476349</v>
       </c>
       <c r="E11" t="n">
-        <v>283459962.576668</v>
+        <v>283082526.8781308</v>
       </c>
       <c r="F11" t="n">
-        <v>248530025.1866648</v>
+        <v>248084201.8837798</v>
       </c>
       <c r="G11" t="n">
-        <v>272554830.575727</v>
+        <v>273569503.5558649</v>
       </c>
       <c r="H11" t="n">
-        <v>283067803.3561054</v>
+        <v>282653892.9764057</v>
       </c>
       <c r="I11" t="n">
-        <v>248528080.6352964</v>
+        <v>278423913.4404849</v>
       </c>
       <c r="J11" t="n">
-        <v>272461453.0282019</v>
+        <v>309766852.7001323</v>
+      </c>
+      <c r="K11" t="n">
+        <v>282660448.7691429</v>
+      </c>
+      <c r="L11" t="n">
+        <v>278776881.2852021</v>
+      </c>
+      <c r="M11" t="n">
+        <v>310036598.3436395</v>
+      </c>
+      <c r="N11" t="n">
+        <v>282143894.011813</v>
+      </c>
+      <c r="O11" t="n">
+        <v>261374630.1921079</v>
+      </c>
+      <c r="P11" t="n">
+        <v>293700082.171069</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>282475141.1563888</v>
+      </c>
+      <c r="R11" t="n">
+        <v>278201683.958708</v>
+      </c>
+      <c r="S11" t="n">
+        <v>309704425.4714556</v>
       </c>
     </row>
     <row r="12">
@@ -824,22 +1106,49 @@
         <v>1244174866.551081</v>
       </c>
       <c r="E12" t="n">
-        <v>2135008313.969743</v>
+        <v>2140000671.49061</v>
       </c>
       <c r="F12" t="n">
-        <v>1644925032.241425</v>
+        <v>1651671041.573342</v>
       </c>
       <c r="G12" t="n">
-        <v>1888640685.437521</v>
+        <v>1752782193.251919</v>
       </c>
       <c r="H12" t="n">
-        <v>2149356154.395647</v>
+        <v>1898921025.348769</v>
       </c>
       <c r="I12" t="n">
-        <v>1637930670.557805</v>
+        <v>1528143879.535588</v>
       </c>
       <c r="J12" t="n">
-        <v>1908281795.601261</v>
+        <v>1857302800.295874</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1899973641.711574</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1522355892.234545</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1858066419.851462</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1895572054.054391</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1538465087.735497</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1875934788.817014</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1895345519.030916</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1528230365.520528</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1860004974.524838</v>
       </c>
     </row>
     <row r="13">
@@ -858,22 +1167,49 @@
         <v>6.984919309616089e-10</v>
       </c>
       <c r="E13" t="n">
-        <v>958811452.0813925</v>
+        <v>960259133.2546607</v>
       </c>
       <c r="F13" t="n">
-        <v>479405726.0406976</v>
+        <v>480129566.6273299</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.405612945556641e-05</v>
+        <v>0.0001227259635925293</v>
       </c>
       <c r="H13" t="n">
-        <v>958412930.2763499</v>
+        <v>1219062894.373544</v>
       </c>
       <c r="I13" t="n">
-        <v>479206465.1381789</v>
+        <v>550621560.5282401</v>
       </c>
       <c r="J13" t="n">
-        <v>8.589029312133789e-05</v>
+        <v>-0.0001786947250366211</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1217455534.811985</v>
+      </c>
+      <c r="L13" t="n">
+        <v>553246171.7495354</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.60472297668457e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1224543403.411634</v>
+      </c>
+      <c r="O13" t="n">
+        <v>612271701.7058192</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.84178352355957e-05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1222382432.036438</v>
+      </c>
+      <c r="R13" t="n">
+        <v>550308585.6604959</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.0001024007797241211</v>
       </c>
     </row>
     <row r="14">
@@ -909,6 +1245,33 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -929,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>31.23874612452493</v>
+        <v>30.66265444170187</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -938,9 +1301,36 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>30.79898601795348</v>
+        <v>28.8808010271614</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>28.98939820363182</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>29.78074452050565</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>28.88486477655204</v>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -960,22 +1350,49 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>341.9117647057568</v>
+        <v>341.9117647058856</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>308.3342576397065</v>
+        <v>307.6066830596367</v>
       </c>
       <c r="H16" t="n">
-        <v>341.9117647059074</v>
+        <v>68.17554510250608</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>173.1306319250344</v>
       </c>
       <c r="J16" t="n">
-        <v>308.8220488978807</v>
+        <v>447.4508624846864</v>
+      </c>
+      <c r="K16" t="n">
+        <v>68.26369134670769</v>
+      </c>
+      <c r="L16" t="n">
+        <v>174.1433703627354</v>
+      </c>
+      <c r="M16" t="n">
+        <v>446.3497624149663</v>
+      </c>
+      <c r="N16" t="n">
+        <v>61.31832808698516</v>
+      </c>
+      <c r="O16" t="n">
+        <v>208.7491631003727</v>
+      </c>
+      <c r="P16" t="n">
+        <v>418.7063041139873</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>65.77212841594027</v>
+      </c>
+      <c r="R16" t="n">
+        <v>173.6726633965321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>449.3181205109814</v>
       </c>
     </row>
     <row r="17">
@@ -1000,15 +1417,42 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9000000000000002</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.8358904109589042</v>
       </c>
       <c r="J17" t="n">
+        <v>0.899999999999927</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8309589041095914</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9000000000000246</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8383561643835618</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.9000000000000001</v>
       </c>
     </row>
@@ -1028,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>562.8218706657963</v>
+        <v>561.5822221602087</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1037,12 +1481,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>563.6529740625984</v>
+        <v>628.4399946279862</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>628.4396276472496</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>628.4685432995905</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>628.4500007831839</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>447.4132813238015</v>
+        <v>446.6128995713386</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1071,12 +1542,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>447.9498850386934</v>
+        <v>489.7523643563492</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>489.7521274147881</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>489.7707968695182</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>489.7588248505517</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1099,19 +1597,46 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>90.27155191597119</v>
+        <v>91.45155468897859</v>
       </c>
       <c r="G20" t="n">
-        <v>94.0731954189677</v>
+        <v>92.686925252547</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>91.9419661638624</v>
+        <v>49.08253415074724</v>
       </c>
       <c r="J20" t="n">
-        <v>92.54106999281156</v>
+        <v>146.1800865509691</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>49.36964549783549</v>
+      </c>
+      <c r="M20" t="n">
+        <v>145.8929141414346</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>59.18038773895567</v>
+      </c>
+      <c r="P20" t="n">
+        <v>136.0869832289757</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>49.23620007291687</v>
+      </c>
+      <c r="S20" t="n">
+        <v>146.0280855707823</v>
       </c>
     </row>
     <row r="21">
@@ -1145,6 +1670,33 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1169,6 +1721,21 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1191,6 +1758,21 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1223,6 +1805,33 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1247,6 +1856,21 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1269,6 +1893,21 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1303,6 +1942,33 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1320,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3402.393168290814</v>
+        <v>3390.919662994996</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1329,12 +1995,39 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3410.085404584127</v>
+        <v>4009.693604201013</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4009.690207640946</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4009.95783503447</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4009.786215648008</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1357,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>898.9567230079117</v>
+        <v>882.3785450849458</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1366,9 +2059,36 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>886.3017559123302</v>
+        <v>831.1021878319827</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>834.227286435448</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>856.9998423166591</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>831.2191302604904</v>
+      </c>
+      <c r="S29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,6 +2125,33 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1439,6 +2186,33 @@
       <c r="J31" t="n">
         <v>1248</v>
       </c>
+      <c r="K31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1248</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1473,6 +2247,33 @@
       <c r="J32" t="n">
         <v>0</v>
       </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1507,6 +2308,33 @@
       <c r="J33" t="n">
         <v>0</v>
       </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1524,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>633.727299228441</v>
+        <v>631.9615152898622</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1533,12 +2361,39 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>634.9111420862039</v>
+        <v>639.0483809032239</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>639.0762412593944</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>636.8810224137239</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>638.2887337243583</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1558,22 +2413,49 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>636.2475224704585</v>
+        <v>634.1019769800862</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>93.20756901573729</v>
+        <v>92.28622388523175</v>
       </c>
       <c r="H35" t="n">
-        <v>637.6859706572318</v>
+        <v>749.8127039855516</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>216.1831875557979</v>
       </c>
       <c r="J35" t="n">
-        <v>94.19869635446793</v>
+        <v>138.4859944824156</v>
+      </c>
+      <c r="K35" t="n">
+        <v>749.8120688291987</v>
+      </c>
+      <c r="L35" t="n">
+        <v>215.7660056297901</v>
+      </c>
+      <c r="M35" t="n">
+        <v>138.6297215593353</v>
+      </c>
+      <c r="N35" t="n">
+        <v>749.8621151513892</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>138.7977202066767</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>749.8300223261588</v>
+      </c>
+      <c r="R35" t="n">
+        <v>216.5422485129129</v>
+      </c>
+      <c r="S35" t="n">
+        <v>138.621572251962</v>
       </c>
     </row>
     <row r="36">
@@ -1597,6 +2479,21 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1619,6 +2516,21 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1653,6 +2565,33 @@
       <c r="J38" t="n">
         <v>0</v>
       </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1670,22 +2609,49 @@
         <v>0.9104843470844927</v>
       </c>
       <c r="E39" t="n">
-        <v>123.8332964336685</v>
+        <v>123.7693103298519</v>
       </c>
       <c r="F39" t="n">
-        <v>2.944967112237537</v>
+        <v>3.364800021549164</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>123.7710689391406</v>
+        <v>125.0517039439625</v>
       </c>
       <c r="I39" t="n">
-        <v>3.603496139868896</v>
+        <v>0.03210577992056631</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1.948449422016889</v>
+      </c>
+      <c r="K39" t="n">
+        <v>125.2900844242975</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0381733010520332</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.775524816268633</v>
+      </c>
+      <c r="N39" t="n">
+        <v>125.188003142124</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.04913547784728346</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>125.0364448010088</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.927088124340266</v>
       </c>
     </row>
     <row r="40">
@@ -1719,6 +2685,33 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1743,6 +2736,21 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1765,6 +2773,21 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1795,6 +2818,27 @@
         <v>0</v>
       </c>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>1068</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="n">
+        <v>1068</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1825,6 +2869,27 @@
         <v>0</v>
       </c>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1842,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>244.5529130280231</v>
+        <v>249.2509072095275</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1851,12 +2916,39 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>53.19829325369167</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1876,7 +2968,7 @@
         <v>29674.51371381121</v>
       </c>
       <c r="E46" t="n">
-        <v>31.95250735716511</v>
+        <v>8.76098891228577</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1885,12 +2977,39 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>46.72990618661598</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>317.4092914009748</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>549.6349635423107</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>8.255911621932086</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>496.2212065343023</v>
+      </c>
+      <c r="S46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1910,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.35190168927353e-09</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.319764047871789e-10</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1925,6 +3044,33 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-5.676529180342172e-10</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-1.449791956994586e-10</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1947,19 +3093,46 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>180.3263708008677</v>
+        <v>176.9884824070306</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6959254149722043</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>177.7718833223215</v>
+        <v>166.5903642822286</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7020908847563903</v>
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>167.215375232173</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.7723989191460324</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>171.8879717203888</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.6854963253386483</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>166.6156838444005</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.7663399696356979</v>
       </c>
     </row>
     <row r="49">
@@ -1978,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4906.997937566995</v>
+        <v>4894.724050517501</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1987,12 +3160,39 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>4915.226777574122</v>
+        <v>5567.445968556478</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5567.442335060588</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5567.728631903989</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5567.545040498673</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2029,6 +3229,33 @@
       <c r="J50" t="n">
         <v>0</v>
       </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2046,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>636.2475224696036</v>
+        <v>634.1019769800862</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2055,12 +3282,39 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>637.6859706572318</v>
+        <v>749.8127039855516</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>749.8120688291987</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>749.8621151513892</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>749.8300223262867</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2097,6 +3351,33 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2114,22 +3395,49 @@
         <v>214.2356823779513</v>
       </c>
       <c r="E53" t="n">
-        <v>194.7599965319801</v>
+        <v>171.568478058439</v>
       </c>
       <c r="F53" t="n">
-        <v>239.2374111180742</v>
+        <v>203.2182975778263</v>
       </c>
       <c r="G53" t="n">
-        <v>473.8750536203616</v>
+        <v>450.3473552046502</v>
       </c>
       <c r="H53" t="n">
-        <v>209.5373953311275</v>
+        <v>90.01574826991836</v>
       </c>
       <c r="I53" t="n">
-        <v>242.1481445675266</v>
+        <v>98.74842076673121</v>
       </c>
       <c r="J53" t="n">
-        <v>488.4756598288935</v>
+        <v>742</v>
+      </c>
+      <c r="K53" t="n">
+        <v>90.03972406059756</v>
+      </c>
+      <c r="L53" t="n">
+        <v>99.72561637311669</v>
+      </c>
+      <c r="M53" t="n">
+        <v>742</v>
+      </c>
+      <c r="N53" t="n">
+        <v>88.15058524401752</v>
+      </c>
+      <c r="O53" t="n">
+        <v>171.6494601726411</v>
+      </c>
+      <c r="P53" t="n">
+        <v>475.4754683756951</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>89.36201893698373</v>
+      </c>
+      <c r="R53" t="n">
+        <v>98.26748584799869</v>
+      </c>
+      <c r="S53" t="n">
+        <v>742</v>
       </c>
     </row>
     <row r="54">
@@ -2151,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>4.523315055848798e-11</v>
+        <v>2.734878989940626e-09</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2164,6 +3472,33 @@
       </c>
       <c r="J54" t="n">
         <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5.800927738164319e-09</v>
       </c>
     </row>
     <row r="55">
@@ -2199,6 +3534,33 @@
       <c r="J55" t="n">
         <v>0</v>
       </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2233,6 +3595,33 @@
       <c r="J56" t="n">
         <v>0</v>
       </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2267,6 +3656,33 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2301,6 +3717,33 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2335,6 +3778,33 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2352,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>3.678194559210924e-10</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2367,6 +3837,33 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.978285796366962e-10</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2403,6 +3900,33 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2437,6 +3961,33 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2454,22 +4005,49 @@
         <v>128.0211414631145</v>
       </c>
       <c r="E63" t="n">
-        <v>123.8332964336685</v>
+        <v>123.7693103298519</v>
       </c>
       <c r="F63" t="n">
-        <v>126.7782635459229</v>
+        <v>127.1341103514831</v>
       </c>
       <c r="G63" t="n">
-        <v>126.778263545906</v>
+        <v>127.1341103514011</v>
       </c>
       <c r="H63" t="n">
-        <v>123.7710689391406</v>
+        <v>125.0517039439625</v>
       </c>
       <c r="I63" t="n">
-        <v>127.3745650790109</v>
+        <v>125.083809723883</v>
       </c>
       <c r="J63" t="n">
-        <v>127.3745650790382</v>
+        <v>127.0322591459063</v>
+      </c>
+      <c r="K63" t="n">
+        <v>125.2900844242975</v>
+      </c>
+      <c r="L63" t="n">
+        <v>125.328257725356</v>
+      </c>
+      <c r="M63" t="n">
+        <v>127.1037825416182</v>
+      </c>
+      <c r="N63" t="n">
+        <v>125.188003142124</v>
+      </c>
+      <c r="O63" t="n">
+        <v>125.1880031421448</v>
+      </c>
+      <c r="P63" t="n">
+        <v>125.2371386199713</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>125.0364448010088</v>
+      </c>
+      <c r="R63" t="n">
+        <v>125.0364448010088</v>
+      </c>
+      <c r="S63" t="n">
+        <v>126.963532925349</v>
       </c>
     </row>
     <row r="64">
@@ -2505,6 +4083,33 @@
       <c r="J64" t="n">
         <v>0</v>
       </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -2522,22 +4127,49 @@
         <v>140.7223740019584</v>
       </c>
       <c r="E65" t="n">
-        <v>135.1598173521924</v>
+        <v>135.1598173518107</v>
       </c>
       <c r="F65" t="n">
-        <v>151.0247294653292</v>
+        <v>148.2395955742709</v>
       </c>
       <c r="G65" t="n">
-        <v>151.0247294653292</v>
+        <v>135.2317777651395</v>
       </c>
       <c r="H65" t="n">
-        <v>135.1598173515981</v>
+        <v>136.5416640005274</v>
       </c>
       <c r="I65" t="n">
-        <v>148.8986949932715</v>
+        <v>139.6251675557731</v>
       </c>
       <c r="J65" t="n">
-        <v>148.8986949932718</v>
+        <v>135.3275188282557</v>
+      </c>
+      <c r="K65" t="n">
+        <v>136.541664001493</v>
+      </c>
+      <c r="L65" t="n">
+        <v>140.1501841211553</v>
+      </c>
+      <c r="M65" t="n">
+        <v>140.1501841211557</v>
+      </c>
+      <c r="N65" t="n">
+        <v>136.5416640007739</v>
+      </c>
+      <c r="O65" t="n">
+        <v>143.9759735093549</v>
+      </c>
+      <c r="P65" t="n">
+        <v>143.9759735092072</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>136.5416640002627</v>
+      </c>
+      <c r="R65" t="n">
+        <v>139.6448138837624</v>
+      </c>
+      <c r="S65" t="n">
+        <v>139.6448138837627</v>
       </c>
     </row>
     <row r="66">
@@ -2556,22 +4188,49 @@
         <v>553.0795362339358</v>
       </c>
       <c r="E66" t="n">
-        <v>341.911764705757</v>
+        <v>341.911764706088</v>
       </c>
       <c r="F66" t="n">
-        <v>318.4181725431082</v>
+        <v>322.5804398200303</v>
       </c>
       <c r="G66" t="n">
-        <v>650.2460223454636</v>
+        <v>649.5184477655223</v>
       </c>
       <c r="H66" t="n">
-        <v>341.9117647065966</v>
+        <v>68.17554510297653</v>
       </c>
       <c r="I66" t="n">
-        <v>324.3102862922836</v>
+        <v>241.3061770275405</v>
       </c>
       <c r="J66" t="n">
-        <v>650.7338136037881</v>
+        <v>688.7570395122268</v>
+      </c>
+      <c r="K66" t="n">
+        <v>68.26369134670769</v>
+      </c>
+      <c r="L66" t="n">
+        <v>242.4070617094446</v>
+      </c>
+      <c r="M66" t="n">
+        <v>688.7568241244096</v>
+      </c>
+      <c r="N66" t="n">
+        <v>61.31832808721716</v>
+      </c>
+      <c r="O66" t="n">
+        <v>208.7491631003727</v>
+      </c>
+      <c r="P66" t="n">
+        <v>688.7737953013452</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>65.77212841663683</v>
+      </c>
+      <c r="R66" t="n">
+        <v>239.4447918124725</v>
+      </c>
+      <c r="S66" t="n">
+        <v>688.7629123234539</v>
       </c>
     </row>
     <row r="67">
@@ -2607,6 +4266,33 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -2641,6 +4327,33 @@
       <c r="J68" t="n">
         <v>0</v>
       </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -2675,6 +4388,33 @@
       <c r="J69" t="n">
         <v>0</v>
       </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -2692,22 +4432,49 @@
         <v>4600</v>
       </c>
       <c r="E70" t="n">
-        <v>1900.000000000099</v>
+        <v>1900</v>
       </c>
       <c r="F70" t="n">
-        <v>3250.000000005721</v>
+        <v>3250</v>
       </c>
       <c r="G70" t="n">
-        <v>3260.806071943854</v>
+        <v>3339.836168007406</v>
       </c>
       <c r="H70" t="n">
-        <v>1713.897924410392</v>
+        <v>1900</v>
       </c>
       <c r="I70" t="n">
         <v>3250</v>
       </c>
       <c r="J70" t="n">
-        <v>3085.867429982203</v>
+        <v>3308.694524937604</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1900</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3250.000000003165</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3326.869140791462</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1900.000000008071</v>
+      </c>
+      <c r="O70" t="n">
+        <v>3250.000000000253</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3048.630795514703</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1900</v>
+      </c>
+      <c r="R70" t="n">
+        <v>3250.000000001914</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3307.543156914411</v>
       </c>
     </row>
     <row r="71">
@@ -2743,6 +4510,33 @@
       <c r="J71" t="n">
         <v>0</v>
       </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -2777,6 +4571,33 @@
       <c r="J72" t="n">
         <v>0</v>
       </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -2811,6 +4632,33 @@
       <c r="J73" t="n">
         <v>0</v>
       </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -2845,6 +4693,33 @@
       <c r="J74" t="n">
         <v>0</v>
       </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -2862,22 +4737,49 @@
         <v>80.71197007483882</v>
       </c>
       <c r="E75" t="n">
-        <v>84.02925771341555</v>
+        <v>83.51406668527662</v>
       </c>
       <c r="F75" t="n">
-        <v>85.05181262147983</v>
+        <v>84.8334262788718</v>
       </c>
       <c r="G75" t="n">
-        <v>158.6617860542663</v>
+        <v>162.5705129215504</v>
       </c>
       <c r="H75" t="n">
-        <v>84.47978566513487</v>
+        <v>84.55616499232698</v>
       </c>
       <c r="I75" t="n">
-        <v>86.20323114519084</v>
+        <v>79.6168200600173</v>
       </c>
       <c r="J75" t="n">
-        <v>159.5533673581964</v>
+        <v>103.9524498431996</v>
+      </c>
+      <c r="K75" t="n">
+        <v>84.32692270918696</v>
+      </c>
+      <c r="L75" t="n">
+        <v>80.05071805705811</v>
+      </c>
+      <c r="M75" t="n">
+        <v>104.5943926808938</v>
+      </c>
+      <c r="N75" t="n">
+        <v>83.70897220961807</v>
+      </c>
+      <c r="O75" t="n">
+        <v>87.68225279554549</v>
+      </c>
+      <c r="P75" t="n">
+        <v>92.83459586251395</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>84.32225986075926</v>
+      </c>
+      <c r="R75" t="n">
+        <v>85.67973890115324</v>
+      </c>
+      <c r="S75" t="n">
+        <v>103.7797473600379</v>
       </c>
     </row>
     <row r="76">
@@ -2913,6 +4815,33 @@
       <c r="J76" t="n">
         <v>0</v>
       </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -2947,6 +4876,33 @@
       <c r="J77" t="n">
         <v>0</v>
       </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -2981,6 +4937,33 @@
       <c r="J78" t="n">
         <v>0</v>
       </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -3015,6 +4998,33 @@
       <c r="J79" t="n">
         <v>0</v>
       </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -3032,22 +5042,49 @@
         <v>322.7818378213971</v>
       </c>
       <c r="E80" t="n">
-        <v>4906.997937566995</v>
+        <v>4894.72405051778</v>
       </c>
       <c r="F80" t="n">
-        <v>2325.2694106536</v>
+        <v>2302.830337963525</v>
       </c>
       <c r="G80" t="n">
-        <v>1360.957267316326</v>
+        <v>1356.367865197998</v>
       </c>
       <c r="H80" t="n">
-        <v>4915.226777574123</v>
+        <v>5567.445968557998</v>
       </c>
       <c r="I80" t="n">
-        <v>2314.68594430636</v>
+        <v>2107.171253981555</v>
       </c>
       <c r="J80" t="n">
-        <v>1364.034161833651</v>
+        <v>1603.877441680406</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5567.442335060588</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2111.688155545567</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1603.876083056379</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5567.728631903989</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2633.370317160141</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1603.983134013788</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5567.545040501011</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2093.836852225465</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1603.914486259205</v>
       </c>
     </row>
     <row r="81">
@@ -3083,6 +5120,33 @@
       <c r="J81" t="n">
         <v>0</v>
       </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3117,6 +5181,33 @@
       <c r="J82" t="n">
         <v>0</v>
       </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -3151,6 +5242,33 @@
       <c r="J83" t="n">
         <v>0</v>
       </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -3185,6 +5303,33 @@
       <c r="J84" t="n">
         <v>0</v>
       </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -3219,6 +5364,33 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3253,6 +5425,33 @@
       <c r="J86" t="n">
         <v>0</v>
       </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -3287,6 +5486,33 @@
       <c r="J87" t="n">
         <v>0</v>
       </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -3321,6 +5547,33 @@
       <c r="J88" t="n">
         <v>0</v>
       </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -3355,6 +5608,33 @@
       <c r="J89" t="n">
         <v>0</v>
       </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -3389,6 +5669,33 @@
       <c r="J90" t="n">
         <v>0</v>
       </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -3406,10 +5713,10 @@
         <v>11.40819763542083</v>
       </c>
       <c r="E91" t="n">
-        <v>8.241015236517838e-11</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>9.703403100380058</v>
+        <v>10.16427644663851</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3418,9 +5725,36 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>10.05521118563723</v>
+        <v>11.58975917827088</v>
       </c>
       <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>11.50288143709454</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>4.816431602776302e-10</v>
+      </c>
+      <c r="O91" t="n">
+        <v>10.86980438359549</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>11.58650817875836</v>
+      </c>
+      <c r="S91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3457,6 +5791,33 @@
       <c r="J92" t="n">
         <v>0</v>
       </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -3491,6 +5852,33 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -3525,6 +5913,33 @@
       <c r="J94" t="n">
         <v>0</v>
       </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -3559,6 +5974,33 @@
       <c r="J95" t="n">
         <v>0</v>
       </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3593,6 +6035,33 @@
       <c r="J96" t="n">
         <v>0</v>
       </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -3627,6 +6096,33 @@
       <c r="J97" t="n">
         <v>0</v>
       </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -3661,6 +6157,33 @@
       <c r="J98" t="n">
         <v>0</v>
       </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -3678,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>3.183231456205249e-12</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3693,6 +6216,33 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>2.867750481527764e-11</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3729,6 +6279,33 @@
       <c r="J100" t="n">
         <v>0</v>
       </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -3763,6 +6340,33 @@
       <c r="J101" t="n">
         <v>0</v>
       </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -3797,6 +6401,33 @@
       <c r="J102" t="n">
         <v>0</v>
       </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -3829,6 +6460,33 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3847,17 +6505,38 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>562.8218706657963</v>
+        <v>561.5822221602087</v>
       </c>
       <c r="G104" t="n">
-        <v>562.8218706657963</v>
+        <v>561.5822221602087</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>563.6529740625984</v>
+        <v>628.4399946279862</v>
       </c>
       <c r="J104" t="n">
-        <v>563.6529740625984</v>
+        <v>628.4399946279862</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>628.4396276472496</v>
+      </c>
+      <c r="M104" t="n">
+        <v>628.4396276472496</v>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>628.4685432995905</v>
+      </c>
+      <c r="P104" t="n">
+        <v>628.4685432995905</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>628.4500007831839</v>
+      </c>
+      <c r="S104" t="n">
+        <v>628.4500007831839</v>
       </c>
     </row>
     <row r="105">
@@ -3875,17 +6554,38 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>447.4132813238015</v>
+        <v>446.6128995713386</v>
       </c>
       <c r="G105" t="n">
-        <v>447.4132813238015</v>
+        <v>446.6128995713386</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>447.9498850386934</v>
+        <v>489.7523643563492</v>
       </c>
       <c r="J105" t="n">
-        <v>447.9498850386934</v>
+        <v>489.7523643563492</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>489.7521274147881</v>
+      </c>
+      <c r="M105" t="n">
+        <v>489.7521274147881</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="n">
+        <v>489.7707968695182</v>
+      </c>
+      <c r="P105" t="n">
+        <v>489.7707968695182</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>489.7588248505517</v>
+      </c>
+      <c r="S105" t="n">
+        <v>489.7588248505517</v>
       </c>
     </row>
     <row r="106">
@@ -3903,17 +6603,38 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>181.8929268666013</v>
+        <v>181.775865894788</v>
       </c>
       <c r="G106" t="n">
-        <v>4.20220793331602</v>
+        <v>11.08091653735357</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>183.5043859832496</v>
+        <v>200.7599372248457</v>
       </c>
       <c r="J106" t="n">
-        <v>3.808390595043647</v>
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>201.8806859288623</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="n">
+        <v>179.1670922499455</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>200.2970678362381</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3941,6 +6662,27 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3963,6 +6705,15 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -3979,17 +6730,38 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>123.8332964336685</v>
+        <v>123.7693103298519</v>
       </c>
       <c r="G109" t="n">
-        <v>126.778263545906</v>
+        <v>127.1341103514011</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>123.7710689391406</v>
+        <v>125.0517039439625</v>
       </c>
       <c r="J109" t="n">
-        <v>127.3745650790095</v>
+        <v>125.083809723883</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>125.2900844242975</v>
+      </c>
+      <c r="M109" t="n">
+        <v>125.3282577253495</v>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>125.188003142124</v>
+      </c>
+      <c r="P109" t="n">
+        <v>125.188003142124</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="n">
+        <v>125.0364448010088</v>
+      </c>
+      <c r="S109" t="n">
+        <v>125.0364448010088</v>
       </c>
     </row>
     <row r="110">
@@ -4007,17 +6779,38 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>4906.997937566995</v>
+        <v>4894.724050517501</v>
       </c>
       <c r="G110" t="n">
-        <v>4906.997937566995</v>
+        <v>4894.724050517501</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>4915.226777574122</v>
+        <v>5567.445968556478</v>
       </c>
       <c r="J110" t="n">
-        <v>4915.226777574122</v>
+        <v>5567.445968556478</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>5567.442335060588</v>
+      </c>
+      <c r="M110" t="n">
+        <v>5567.442335060588</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>5567.728631903989</v>
+      </c>
+      <c r="P110" t="n">
+        <v>5567.728631903989</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>5567.545040498673</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5567.545040498673</v>
       </c>
     </row>
     <row r="111">
@@ -4037,6 +6830,15 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4051,17 +6853,38 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>341.9117647057568</v>
+        <v>341.9117647058856</v>
       </c>
       <c r="G112" t="n">
-        <v>341.9117647057568</v>
+        <v>341.9117647058856</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>341.9117647059074</v>
+        <v>68.17554510250608</v>
       </c>
       <c r="J112" t="n">
-        <v>341.9117647059074</v>
+        <v>241.3061770275404</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>68.26369134670769</v>
+      </c>
+      <c r="M112" t="n">
+        <v>242.4070617094431</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>61.31832808698516</v>
+      </c>
+      <c r="P112" t="n">
+        <v>270.0674911873579</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>65.77212841594027</v>
+      </c>
+      <c r="S112" t="n">
+        <v>239.4447918124724</v>
       </c>
     </row>
     <row r="113">
@@ -4080,14 +6903,35 @@
         <v>0.9000000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
         <v>0.9</v>
       </c>
-      <c r="J113" t="n">
-        <v>0.9000000000000001</v>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.9000000000000155</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="114">
@@ -4104,12 +6948,27 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>90.27155191597119</v>
+        <v>91.45155468897859</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>91.9419661638624</v>
+        <v>49.08253415074724</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>49.36964549783549</v>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>59.18038773895567</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="n">
+        <v>49.23620007291687</v>
       </c>
     </row>
     <row r="115">
@@ -4126,12 +6985,27 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>181.8929268666013</v>
+        <v>181.775865894788</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>183.5043859832496</v>
+        <v>200.7599372248457</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>201.8806859288623</v>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>179.1670922499455</v>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="n">
+        <v>200.2970678362381</v>
       </c>
     </row>
     <row r="116">
@@ -4151,6 +7025,15 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -4165,17 +7048,38 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>633.727299228441</v>
+        <v>631.9615152898622</v>
       </c>
       <c r="G117" t="n">
-        <v>633.727299228441</v>
+        <v>631.9615152898622</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>634.9111420862039</v>
+        <v>639.0483809032239</v>
       </c>
       <c r="J117" t="n">
-        <v>634.9111420862039</v>
+        <v>639.0483809032239</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>639.0762412593944</v>
+      </c>
+      <c r="M117" t="n">
+        <v>639.0762412593944</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="n">
+        <v>636.8810224137239</v>
+      </c>
+      <c r="P117" t="n">
+        <v>636.8810224137239</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>638.2887337243583</v>
+      </c>
+      <c r="S117" t="n">
+        <v>638.2887337243583</v>
       </c>
     </row>
     <row r="118">
@@ -4191,17 +7095,30 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>31.95250735716511</v>
+        <v>8.76098891228577</v>
       </c>
       <c r="G118" t="n">
-        <v>31.95250735716511</v>
+        <v>8.76098891228577</v>
       </c>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="n">
-        <v>46.72990618661598</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
-        <v>46.72990618661598</v>
+        <v>317.4092914009748</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>549.6349635423107</v>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>8.255911621932086</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="n">
+        <v>496.2212065343023</v>
       </c>
     </row>
     <row r="119">
@@ -4221,6 +7138,15 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -4233,17 +7159,38 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>3402.393168290814</v>
+        <v>3390.919662994996</v>
       </c>
       <c r="G120" t="n">
-        <v>3402.393168290814</v>
+        <v>3390.919662994996</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>3410.085404584127</v>
+        <v>4009.693604201013</v>
       </c>
       <c r="J120" t="n">
-        <v>3410.085404584127</v>
+        <v>4009.693604201013</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>4009.690207640946</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4009.690207640946</v>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="n">
+        <v>4009.95783503447</v>
+      </c>
+      <c r="P120" t="n">
+        <v>4009.95783503447</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>4009.786215648008</v>
+      </c>
+      <c r="S120" t="n">
+        <v>4009.786215648008</v>
       </c>
     </row>
     <row r="121">
@@ -4257,17 +7204,38 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>636.2475224704585</v>
+        <v>634.1019769800862</v>
       </c>
       <c r="G121" t="n">
-        <v>636.2475224704585</v>
+        <v>634.1019769800862</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>637.6859706572318</v>
+        <v>749.8127039855516</v>
       </c>
       <c r="J121" t="n">
-        <v>637.6859706572318</v>
+        <v>965.9958915413495</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>749.8120688291987</v>
+      </c>
+      <c r="M121" t="n">
+        <v>965.5780744589888</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="n">
+        <v>749.8621151513892</v>
+      </c>
+      <c r="P121" t="n">
+        <v>749.8621151513892</v>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>749.8300223261588</v>
+      </c>
+      <c r="S121" t="n">
+        <v>966.3722708390717</v>
       </c>
     </row>
     <row r="122">
@@ -4281,18 +7249,23 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>244.5529130280231</v>
+        <v>249.2509072095275</v>
       </c>
       <c r="G122" t="n">
-        <v>244.5529130280231</v>
+        <v>249.2509072095275</v>
       </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
-        <v>53.19829325369167</v>
-      </c>
-      <c r="J122" t="n">
-        <v>53.19829325369167</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -4305,17 +7278,38 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>636.2475224696036</v>
+        <v>634.1019769800862</v>
       </c>
       <c r="G123" t="n">
-        <v>636.2475224696036</v>
+        <v>634.1019769800862</v>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>637.6859706572318</v>
+        <v>749.8127039855516</v>
       </c>
       <c r="J123" t="n">
-        <v>637.6859706572318</v>
+        <v>749.8127039855516</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>749.8120688291987</v>
+      </c>
+      <c r="M123" t="n">
+        <v>749.8120688291987</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="n">
+        <v>749.8621151513892</v>
+      </c>
+      <c r="P123" t="n">
+        <v>749.8621151513892</v>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="n">
+        <v>749.8300223262867</v>
+      </c>
+      <c r="S123" t="n">
+        <v>749.8300223262867</v>
       </c>
     </row>
     <row r="124">
@@ -4330,12 +7324,27 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>31.23874612452493</v>
+        <v>30.66265444170187</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
-        <v>30.79898601795348</v>
+        <v>28.8808010271614</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>28.98939820363182</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>29.78074452050565</v>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="n">
+        <v>28.88486477655204</v>
       </c>
     </row>
     <row r="125">
@@ -4350,12 +7359,27 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>898.9567230079117</v>
+        <v>882.3785450849458</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>886.3017559123302</v>
+        <v>831.1021878319827</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>834.227286435448</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>856.9998423166591</v>
+      </c>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="n">
+        <v>831.2191302604904</v>
       </c>
     </row>
     <row r="126">
@@ -4370,19 +7394,37 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>180.3263708008677</v>
+        <v>176.9884824070306</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>177.7718833223215</v>
+        <v>166.5903642822286</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>167.215375232173</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>171.8879717203888</v>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="n">
+        <v>166.6156838444005</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
